--- a/input/SKU主数据.xlsx
+++ b/input/SKU主数据.xlsx
@@ -476,34 +476,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>洗护</t>
+          <t>厨房</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>72.37</v>
+        <v>1396.79</v>
       </c>
       <c r="E2" t="n">
-        <v>131.57</v>
+        <v>2283.76</v>
       </c>
       <c r="F2" t="n">
-        <v>83.23</v>
+        <v>1606.31</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -520,22 +520,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>饮料</t>
+          <t>厨房</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>535.34</v>
+        <v>1152.8</v>
       </c>
       <c r="E3" t="n">
-        <v>761.0700000000001</v>
+        <v>1590.19</v>
       </c>
       <c r="F3" t="n">
-        <v>615.64</v>
+        <v>1325.72</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -543,11 +543,11 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -564,22 +564,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>零食</t>
+          <t>护肤</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>866.72</v>
+        <v>192.62</v>
       </c>
       <c r="E4" t="n">
-        <v>1869.52</v>
+        <v>333.67</v>
       </c>
       <c r="F4" t="n">
-        <v>996.73</v>
+        <v>221.51</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>季节性</t>
+          <t>在售</t>
         </is>
       </c>
     </row>
@@ -608,34 +608,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>奶粉</t>
+          <t>洗护</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>955.48</v>
+        <v>27.46</v>
       </c>
       <c r="E5" t="n">
-        <v>1945.78</v>
+        <v>39.06</v>
       </c>
       <c r="F5" t="n">
-        <v>1098.8</v>
+        <v>31.58</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -652,34 +652,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>小家电</t>
+          <t>彩妆</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>65.76000000000001</v>
+        <v>346.02</v>
       </c>
       <c r="E6" t="n">
-        <v>127.8</v>
+        <v>436.56</v>
       </c>
       <c r="F6" t="n">
-        <v>75.62</v>
+        <v>397.92</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -696,34 +696,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>美妆</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>香水</t>
+          <t>调味</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>418.09</v>
+        <v>12.53</v>
       </c>
       <c r="E7" t="n">
-        <v>747.73</v>
+        <v>18.27</v>
       </c>
       <c r="F7" t="n">
-        <v>480.8</v>
+        <v>14.41</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -740,34 +740,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>小家电</t>
+          <t>香水</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>715.03</v>
+        <v>282.81</v>
       </c>
       <c r="E8" t="n">
-        <v>1380.03</v>
+        <v>401.74</v>
       </c>
       <c r="F8" t="n">
-        <v>822.28</v>
+        <v>325.23</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2023-01-20</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -784,22 +784,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>厨房</t>
+          <t>辅食</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>956</v>
+        <v>111.19</v>
       </c>
       <c r="E9" t="n">
-        <v>1350.52</v>
+        <v>161.84</v>
       </c>
       <c r="F9" t="n">
-        <v>1099.4</v>
+        <v>127.87</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -807,11 +807,11 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -828,22 +828,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>个护</t>
+          <t>饮料</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>367.9</v>
+        <v>16.19</v>
       </c>
       <c r="E10" t="n">
-        <v>739.67</v>
+        <v>28.53</v>
       </c>
       <c r="F10" t="n">
-        <v>423.08</v>
+        <v>18.62</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -851,16 +851,16 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>季节性</t>
+          <t>在售</t>
         </is>
       </c>
     </row>
@@ -872,22 +872,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>玩具</t>
+          <t>工具</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>836.83</v>
+        <v>211.01</v>
       </c>
       <c r="E11" t="n">
-        <v>1141.77</v>
+        <v>306.38</v>
       </c>
       <c r="F11" t="n">
-        <v>962.35</v>
+        <v>242.66</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -895,11 +895,11 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -916,34 +916,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>调味</t>
+          <t>个护</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>961.3200000000001</v>
+        <v>2806</v>
       </c>
       <c r="E12" t="n">
-        <v>1755.69</v>
+        <v>3542.59</v>
       </c>
       <c r="F12" t="n">
-        <v>1105.52</v>
+        <v>3226.9</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -965,29 +965,29 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>玩具</t>
+          <t>辅食</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1349.12</v>
+        <v>159.33</v>
       </c>
       <c r="E13" t="n">
-        <v>1948.98</v>
+        <v>207.73</v>
       </c>
       <c r="F13" t="n">
-        <v>1551.49</v>
+        <v>183.23</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1004,26 +1004,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>用品</t>
+          <t>护肤</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>853.39</v>
+        <v>167.52</v>
       </c>
       <c r="E14" t="n">
-        <v>1511.48</v>
+        <v>250.49</v>
       </c>
       <c r="F14" t="n">
-        <v>981.4</v>
+        <v>192.65</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1053,29 +1053,29 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>辅食</t>
+          <t>奶粉</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1228.46</v>
+        <v>182.95</v>
       </c>
       <c r="E15" t="n">
-        <v>1855.24</v>
+        <v>230.14</v>
       </c>
       <c r="F15" t="n">
-        <v>1412.73</v>
+        <v>210.39</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1092,26 +1092,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>调味</t>
+          <t>厨房</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>213.98</v>
+        <v>1944.06</v>
       </c>
       <c r="E16" t="n">
-        <v>511.64</v>
+        <v>2512.55</v>
       </c>
       <c r="F16" t="n">
-        <v>246.08</v>
+        <v>2235.67</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>停售</t>
+          <t>在售</t>
         </is>
       </c>
     </row>
@@ -1136,22 +1136,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>零食</t>
+          <t>洗护</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>268.99</v>
+        <v>43.94</v>
       </c>
       <c r="E17" t="n">
-        <v>366.88</v>
+        <v>60.73</v>
       </c>
       <c r="F17" t="n">
-        <v>309.34</v>
+        <v>50.53</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1159,11 +1159,11 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1180,22 +1180,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>个护</t>
+          <t>家居</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>770.24</v>
+        <v>34.05</v>
       </c>
       <c r="E18" t="n">
-        <v>1609.78</v>
+        <v>60.42</v>
       </c>
       <c r="F18" t="n">
-        <v>885.78</v>
+        <v>39.16</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1203,11 +1203,11 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1224,34 +1224,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>奶粉</t>
+          <t>童装</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>167.59</v>
+        <v>449.79</v>
       </c>
       <c r="E19" t="n">
-        <v>395.25</v>
+        <v>688.4299999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>192.73</v>
+        <v>517.26</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2024-01-13</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1273,21 +1273,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>彩妆</t>
+          <t>工具</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>627.71</v>
+        <v>125.39</v>
       </c>
       <c r="E20" t="n">
-        <v>853.97</v>
+        <v>220.32</v>
       </c>
       <c r="F20" t="n">
-        <v>721.87</v>
+        <v>144.2</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2023-11-30</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1312,34 +1312,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>零食</t>
+          <t>童装</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>165.53</v>
+        <v>237.05</v>
       </c>
       <c r="E21" t="n">
-        <v>399.75</v>
+        <v>279.46</v>
       </c>
       <c r="F21" t="n">
-        <v>190.36</v>
+        <v>272.61</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-01-21</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1356,39 +1356,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>家居</t>
+          <t>辅食</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>761.22</v>
+        <v>311.7</v>
       </c>
       <c r="E22" t="n">
-        <v>1852.75</v>
+        <v>375.37</v>
       </c>
       <c r="F22" t="n">
-        <v>875.4</v>
+        <v>358.45</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -1400,22 +1400,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>家居</t>
+          <t>彩妆</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>766.63</v>
+        <v>91.13</v>
       </c>
       <c r="E23" t="n">
-        <v>1575.65</v>
+        <v>159.68</v>
       </c>
       <c r="F23" t="n">
-        <v>881.62</v>
+        <v>104.8</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1423,16 +1423,16 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -1453,30 +1453,30 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>591.64</v>
+        <v>89.33</v>
       </c>
       <c r="E24" t="n">
-        <v>852.84</v>
+        <v>107.61</v>
       </c>
       <c r="F24" t="n">
-        <v>680.39</v>
+        <v>102.73</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>季节性</t>
+          <t>在售</t>
         </is>
       </c>
     </row>
@@ -1488,34 +1488,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>女装</t>
+          <t>零食</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>837.48</v>
+        <v>18.72</v>
       </c>
       <c r="E25" t="n">
-        <v>1356.32</v>
+        <v>33.45</v>
       </c>
       <c r="F25" t="n">
-        <v>963.1</v>
+        <v>21.53</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1532,34 +1532,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>小家电</t>
+          <t>女装</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>717.1900000000001</v>
+        <v>380.64</v>
       </c>
       <c r="E26" t="n">
-        <v>1483.36</v>
+        <v>565.87</v>
       </c>
       <c r="F26" t="n">
-        <v>824.77</v>
+        <v>437.74</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2023-09-10</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1576,26 +1576,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>纸品</t>
+          <t>用品</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>302.07</v>
+        <v>101.95</v>
       </c>
       <c r="E27" t="n">
-        <v>533.9299999999999</v>
+        <v>130.59</v>
       </c>
       <c r="F27" t="n">
-        <v>347.38</v>
+        <v>117.24</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>季节性</t>
+          <t>在售</t>
         </is>
       </c>
     </row>
@@ -1620,34 +1620,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>数码</t>
+          <t>男装</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>158.61</v>
+        <v>337.07</v>
       </c>
       <c r="E28" t="n">
-        <v>360.44</v>
+        <v>432.28</v>
       </c>
       <c r="F28" t="n">
-        <v>182.4</v>
+        <v>387.63</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1669,21 +1669,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>洗护</t>
+          <t>纸品</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1037.2</v>
+        <v>92.77</v>
       </c>
       <c r="E29" t="n">
-        <v>1417.49</v>
+        <v>109.98</v>
       </c>
       <c r="F29" t="n">
-        <v>1192.78</v>
+        <v>106.69</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1708,26 +1708,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>美妆</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>彩妆</t>
+          <t>清洁</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>447.94</v>
+        <v>34.02</v>
       </c>
       <c r="E30" t="n">
-        <v>795.96</v>
+        <v>45.74</v>
       </c>
       <c r="F30" t="n">
-        <v>515.13</v>
+        <v>39.12</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1752,34 +1752,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>小家电</t>
+          <t>饮料</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>61.46</v>
+        <v>43.45</v>
       </c>
       <c r="E31" t="n">
-        <v>125.51</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>70.68000000000001</v>
+        <v>49.97</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1796,34 +1796,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>纸品</t>
+          <t>玩具</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>512.1</v>
+        <v>163.11</v>
       </c>
       <c r="E32" t="n">
-        <v>967.85</v>
+        <v>192.38</v>
       </c>
       <c r="F32" t="n">
-        <v>588.91</v>
+        <v>187.58</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1840,22 +1840,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>调味</t>
+          <t>童装</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>268.8</v>
+        <v>284.14</v>
       </c>
       <c r="E33" t="n">
-        <v>439.17</v>
+        <v>427.44</v>
       </c>
       <c r="F33" t="n">
-        <v>309.12</v>
+        <v>326.76</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1863,11 +1863,11 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1884,34 +1884,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>厨房</t>
+          <t>洗护</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1357.37</v>
+        <v>89.37</v>
       </c>
       <c r="E34" t="n">
-        <v>1840.98</v>
+        <v>110.21</v>
       </c>
       <c r="F34" t="n">
-        <v>1560.98</v>
+        <v>102.78</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1928,34 +1928,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>男装</t>
+          <t>辅食</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>476.73</v>
+        <v>186.21</v>
       </c>
       <c r="E35" t="n">
-        <v>731.83</v>
+        <v>226.52</v>
       </c>
       <c r="F35" t="n">
-        <v>548.24</v>
+        <v>214.14</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1972,22 +1972,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>零食</t>
+          <t>家居</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1109.21</v>
+        <v>90.72</v>
       </c>
       <c r="E36" t="n">
-        <v>1650.05</v>
+        <v>136.9</v>
       </c>
       <c r="F36" t="n">
-        <v>1275.59</v>
+        <v>104.33</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1995,16 +1995,16 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2023-01-28</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>季节性</t>
+          <t>在售</t>
         </is>
       </c>
     </row>
@@ -2021,21 +2021,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>生鲜</t>
+          <t>调味</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>799.89</v>
+        <v>23.44</v>
       </c>
       <c r="E37" t="n">
-        <v>1749.08</v>
+        <v>31.05</v>
       </c>
       <c r="F37" t="n">
-        <v>919.87</v>
+        <v>26.96</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -2060,39 +2060,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>奶粉</t>
+          <t>零食</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>246.65</v>
+        <v>26.69</v>
       </c>
       <c r="E38" t="n">
-        <v>484.7</v>
+        <v>35.65</v>
       </c>
       <c r="F38" t="n">
-        <v>283.65</v>
+        <v>30.69</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>停售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -2104,22 +2104,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>童装</t>
+          <t>厨房</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>805.63</v>
+        <v>590.3</v>
       </c>
       <c r="E39" t="n">
-        <v>1337.06</v>
+        <v>829.3200000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>926.47</v>
+        <v>678.84</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2127,11 +2127,11 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>生鲜</t>
+          <t>工具</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>599.67</v>
+        <v>205.92</v>
       </c>
       <c r="E40" t="n">
-        <v>827.01</v>
+        <v>276.01</v>
       </c>
       <c r="F40" t="n">
-        <v>689.62</v>
+        <v>236.81</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2171,16 +2171,16 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>季节性</t>
+          <t>在售</t>
         </is>
       </c>
     </row>
@@ -2192,22 +2192,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>调味</t>
+          <t>奶粉</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>356.88</v>
+        <v>215.94</v>
       </c>
       <c r="E41" t="n">
-        <v>593.28</v>
+        <v>330.01</v>
       </c>
       <c r="F41" t="n">
-        <v>410.41</v>
+        <v>248.33</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2215,11 +2215,11 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2236,22 +2236,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>清洁</t>
+          <t>小家电</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>133.06</v>
+        <v>2307.82</v>
       </c>
       <c r="E42" t="n">
-        <v>185.37</v>
+        <v>3823.8</v>
       </c>
       <c r="F42" t="n">
-        <v>153.02</v>
+        <v>2653.99</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2259,11 +2259,11 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2280,39 +2280,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>纸品</t>
+          <t>生鲜</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>827.85</v>
+        <v>17.37</v>
       </c>
       <c r="E43" t="n">
-        <v>1557.99</v>
+        <v>24.43</v>
       </c>
       <c r="F43" t="n">
-        <v>952.03</v>
+        <v>19.98</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -2324,22 +2324,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>数码</t>
+          <t>用品</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>536</v>
+        <v>131.07</v>
       </c>
       <c r="E44" t="n">
-        <v>734.73</v>
+        <v>184.96</v>
       </c>
       <c r="F44" t="n">
-        <v>616.4</v>
+        <v>150.73</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2347,11 +2347,11 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2368,39 +2368,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>数码</t>
+          <t>清洁</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>489.76</v>
+        <v>47.05</v>
       </c>
       <c r="E45" t="n">
-        <v>1043.34</v>
+        <v>61.24</v>
       </c>
       <c r="F45" t="n">
-        <v>563.22</v>
+        <v>54.11</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2023-01-18</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -2412,22 +2412,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>小家电</t>
+          <t>调味</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>834.98</v>
+        <v>27.87</v>
       </c>
       <c r="E46" t="n">
-        <v>1375.06</v>
+        <v>45.19</v>
       </c>
       <c r="F46" t="n">
-        <v>960.23</v>
+        <v>32.05</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2435,16 +2435,16 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2023-03-12</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>停售</t>
         </is>
       </c>
     </row>
@@ -2456,34 +2456,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>家居</t>
+          <t>配件</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1170.83</v>
+        <v>293.37</v>
       </c>
       <c r="E47" t="n">
-        <v>1695.14</v>
+        <v>532.4</v>
       </c>
       <c r="F47" t="n">
-        <v>1346.45</v>
+        <v>337.38</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2500,22 +2500,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>小家电</t>
+          <t>纸品</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>337.43</v>
+        <v>34.58</v>
       </c>
       <c r="E48" t="n">
-        <v>695.74</v>
+        <v>62.1</v>
       </c>
       <c r="F48" t="n">
-        <v>388.04</v>
+        <v>39.77</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2523,11 +2523,11 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2023-01-25</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2544,22 +2544,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>调味</t>
+          <t>厨房</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>66.86</v>
+        <v>379.06</v>
       </c>
       <c r="E49" t="n">
-        <v>103.82</v>
+        <v>592.74</v>
       </c>
       <c r="F49" t="n">
-        <v>76.89</v>
+        <v>435.92</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2588,26 +2588,26 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>清洁</t>
+          <t>玩具</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>889.89</v>
+        <v>299.6</v>
       </c>
       <c r="E50" t="n">
-        <v>1760.22</v>
+        <v>398.38</v>
       </c>
       <c r="F50" t="n">
-        <v>1023.37</v>
+        <v>344.54</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2637,17 +2637,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>数码</t>
+          <t>小家电</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>357.71</v>
+        <v>1338.58</v>
       </c>
       <c r="E51" t="n">
-        <v>559.37</v>
+        <v>1876.52</v>
       </c>
       <c r="F51" t="n">
-        <v>411.37</v>
+        <v>1539.37</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2655,11 +2655,11 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2676,22 +2676,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>调味</t>
+          <t>小家电</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>806.15</v>
+        <v>1613.08</v>
       </c>
       <c r="E52" t="n">
-        <v>1182.15</v>
+        <v>2273.29</v>
       </c>
       <c r="F52" t="n">
-        <v>927.0700000000001</v>
+        <v>1855.04</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2699,16 +2699,16 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>季节性</t>
+          <t>在售</t>
         </is>
       </c>
     </row>
@@ -2720,34 +2720,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>小家电</t>
+          <t>奶粉</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1335.59</v>
+        <v>118.59</v>
       </c>
       <c r="E53" t="n">
-        <v>1967.92</v>
+        <v>148.79</v>
       </c>
       <c r="F53" t="n">
-        <v>1535.93</v>
+        <v>136.38</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -2764,34 +2764,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>美妆</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>彩妆</t>
+          <t>洗护</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>74.52</v>
+        <v>44.36</v>
       </c>
       <c r="E54" t="n">
-        <v>124.6</v>
+        <v>71.06</v>
       </c>
       <c r="F54" t="n">
-        <v>85.7</v>
+        <v>51.01</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -2808,34 +2808,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>数码</t>
+          <t>香水</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>502.76</v>
+        <v>217.04</v>
       </c>
       <c r="E55" t="n">
-        <v>1213.31</v>
+        <v>331.94</v>
       </c>
       <c r="F55" t="n">
-        <v>578.17</v>
+        <v>249.6</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -2861,30 +2861,30 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>424.65</v>
+        <v>122.66</v>
       </c>
       <c r="E56" t="n">
-        <v>724.09</v>
+        <v>193.87</v>
       </c>
       <c r="F56" t="n">
-        <v>488.35</v>
+        <v>141.06</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2023-04-14</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>季节性</t>
+          <t>在售</t>
         </is>
       </c>
     </row>
@@ -2896,34 +2896,34 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>个护</t>
+          <t>护肤</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1000.05</v>
+        <v>244.83</v>
       </c>
       <c r="E57" t="n">
-        <v>1583.53</v>
+        <v>294.54</v>
       </c>
       <c r="F57" t="n">
-        <v>1150.06</v>
+        <v>281.55</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -2945,21 +2945,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>玩具</t>
+          <t>奶粉</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>382.13</v>
+        <v>220.53</v>
       </c>
       <c r="E58" t="n">
-        <v>900.97</v>
+        <v>287.33</v>
       </c>
       <c r="F58" t="n">
-        <v>439.45</v>
+        <v>253.61</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -2984,34 +2984,34 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>辅食</t>
+          <t>调味</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1234.02</v>
+        <v>27.1</v>
       </c>
       <c r="E59" t="n">
-        <v>1969.26</v>
+        <v>46.42</v>
       </c>
       <c r="F59" t="n">
-        <v>1419.12</v>
+        <v>31.16</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3028,34 +3028,34 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>童装</t>
+          <t>生鲜</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>111.42</v>
+        <v>10.72</v>
       </c>
       <c r="E60" t="n">
-        <v>275.51</v>
+        <v>13.52</v>
       </c>
       <c r="F60" t="n">
-        <v>128.13</v>
+        <v>12.33</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2023-01-02</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3077,21 +3077,21 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>奶粉</t>
+          <t>玩具</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>986.84</v>
+        <v>90.81</v>
       </c>
       <c r="E61" t="n">
-        <v>1804.03</v>
+        <v>134.38</v>
       </c>
       <c r="F61" t="n">
-        <v>1134.87</v>
+        <v>104.43</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3116,34 +3116,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>奶粉</t>
+          <t>配件</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>240.43</v>
+        <v>315</v>
       </c>
       <c r="E62" t="n">
-        <v>420.65</v>
+        <v>403.94</v>
       </c>
       <c r="F62" t="n">
-        <v>276.49</v>
+        <v>362.25</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3160,34 +3160,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>小家电</t>
+          <t>家居</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>75.34</v>
+        <v>18.4</v>
       </c>
       <c r="E63" t="n">
-        <v>136.55</v>
+        <v>22.57</v>
       </c>
       <c r="F63" t="n">
-        <v>86.64</v>
+        <v>21.16</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3204,22 +3204,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>洗护</t>
+          <t>男装</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>474.25</v>
+        <v>284.69</v>
       </c>
       <c r="E64" t="n">
-        <v>900.3099999999999</v>
+        <v>513.23</v>
       </c>
       <c r="F64" t="n">
-        <v>545.39</v>
+        <v>327.39</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3227,11 +3227,11 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2024-01-22</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3248,22 +3248,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>洗护</t>
+          <t>辅食</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>757.51</v>
+        <v>158.87</v>
       </c>
       <c r="E65" t="n">
-        <v>1063.84</v>
+        <v>259.66</v>
       </c>
       <c r="F65" t="n">
-        <v>871.14</v>
+        <v>182.7</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3271,11 +3271,11 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2023-03-17</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3292,22 +3292,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>美妆</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>香水</t>
+          <t>用品</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>910.1900000000001</v>
+        <v>175.23</v>
       </c>
       <c r="E66" t="n">
-        <v>1622.7</v>
+        <v>301.98</v>
       </c>
       <c r="F66" t="n">
-        <v>1046.72</v>
+        <v>201.51</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3315,11 +3315,11 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2023-03-13</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>纸品</t>
+          <t>零食</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>630.14</v>
+        <v>14.04</v>
       </c>
       <c r="E67" t="n">
-        <v>1389.37</v>
+        <v>25.06</v>
       </c>
       <c r="F67" t="n">
-        <v>724.66</v>
+        <v>16.15</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3359,11 +3359,11 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3380,34 +3380,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>零食</t>
+          <t>纸品</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>869.52</v>
+        <v>124.37</v>
       </c>
       <c r="E68" t="n">
-        <v>1883.51</v>
+        <v>170.53</v>
       </c>
       <c r="F68" t="n">
-        <v>999.95</v>
+        <v>143.03</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3424,34 +3424,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>童装</t>
+          <t>小家电</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>866.47</v>
+        <v>661.5</v>
       </c>
       <c r="E69" t="n">
-        <v>1487.22</v>
+        <v>869.27</v>
       </c>
       <c r="F69" t="n">
-        <v>996.4400000000001</v>
+        <v>760.72</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3468,34 +3468,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>奶粉</t>
+          <t>清洁</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>272.54</v>
+        <v>18.23</v>
       </c>
       <c r="E70" t="n">
-        <v>434.22</v>
+        <v>32.28</v>
       </c>
       <c r="F70" t="n">
-        <v>313.42</v>
+        <v>20.96</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -3512,26 +3512,26 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>饮料</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>548.49</v>
+        <v>35.62</v>
       </c>
       <c r="E71" t="n">
-        <v>891.03</v>
+        <v>46.13</v>
       </c>
       <c r="F71" t="n">
-        <v>630.76</v>
+        <v>40.96</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H71" t="n">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -3556,22 +3556,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>饮料</t>
+          <t>数码</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1371.77</v>
+        <v>1642.51</v>
       </c>
       <c r="E72" t="n">
-        <v>1900.31</v>
+        <v>2449.03</v>
       </c>
       <c r="F72" t="n">
-        <v>1577.54</v>
+        <v>1888.89</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3579,16 +3579,16 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>季节性</t>
+          <t>在售</t>
         </is>
       </c>
     </row>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>奶粉</t>
+          <t>个护</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1238.56</v>
+        <v>824.26</v>
       </c>
       <c r="E73" t="n">
-        <v>1845.5</v>
+        <v>1328.8</v>
       </c>
       <c r="F73" t="n">
-        <v>1424.34</v>
+        <v>947.9</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3627,12 +3627,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>停售</t>
+          <t>在售</t>
         </is>
       </c>
     </row>
@@ -3644,39 +3644,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>美妆</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>工具</t>
+          <t>洗护</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>711.91</v>
+        <v>61.76</v>
       </c>
       <c r="E74" t="n">
-        <v>1265.15</v>
+        <v>100.4</v>
       </c>
       <c r="F74" t="n">
-        <v>818.7</v>
+        <v>71.02</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>停售</t>
+          <t>在售</t>
         </is>
       </c>
     </row>
@@ -3688,39 +3688,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>零食</t>
+          <t>用品</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>925.76</v>
+        <v>201.47</v>
       </c>
       <c r="E75" t="n">
-        <v>1343.61</v>
+        <v>249</v>
       </c>
       <c r="F75" t="n">
-        <v>1064.62</v>
+        <v>231.69</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>季节性</t>
+          <t>在售</t>
         </is>
       </c>
     </row>
@@ -3732,26 +3732,26 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>调味</t>
+          <t>工具</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>177.97</v>
+        <v>112.22</v>
       </c>
       <c r="E76" t="n">
-        <v>293.02</v>
+        <v>197.94</v>
       </c>
       <c r="F76" t="n">
-        <v>204.67</v>
+        <v>129.05</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H76" t="n">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2024-11-30</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>童装</t>
+          <t>饮料</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>925.66</v>
+        <v>28.95</v>
       </c>
       <c r="E77" t="n">
-        <v>1805.09</v>
+        <v>41.29</v>
       </c>
       <c r="F77" t="n">
-        <v>1064.51</v>
+        <v>33.29</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2023-02-07</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -3820,39 +3820,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>小家电</t>
+          <t>零食</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>504.82</v>
+        <v>13.66</v>
       </c>
       <c r="E78" t="n">
-        <v>1038.89</v>
+        <v>21.45</v>
       </c>
       <c r="F78" t="n">
-        <v>580.54</v>
+        <v>15.71</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>季节性</t>
+          <t>在售</t>
         </is>
       </c>
     </row>
@@ -3864,34 +3864,34 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>彩妆</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>981.9299999999999</v>
+        <v>498.15</v>
       </c>
       <c r="E79" t="n">
-        <v>1350.44</v>
+        <v>626.8099999999999</v>
       </c>
       <c r="F79" t="n">
-        <v>1129.22</v>
+        <v>572.87</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2024-01-04</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -3913,29 +3913,29 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>童装</t>
+          <t>男装</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>341.4</v>
+        <v>120.45</v>
       </c>
       <c r="E80" t="n">
-        <v>686.0599999999999</v>
+        <v>156.54</v>
       </c>
       <c r="F80" t="n">
-        <v>392.61</v>
+        <v>138.52</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -3952,26 +3952,26 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>清洁</t>
+          <t>配件</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>786.23</v>
+        <v>87.17</v>
       </c>
       <c r="E81" t="n">
-        <v>1409.56</v>
+        <v>135</v>
       </c>
       <c r="F81" t="n">
-        <v>904.16</v>
+        <v>100.25</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H81" t="n">
@@ -3979,12 +3979,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -4001,17 +4001,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>生鲜</t>
+          <t>零食</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>749.54</v>
+        <v>14.27</v>
       </c>
       <c r="E82" t="n">
-        <v>1131.1</v>
+        <v>19.56</v>
       </c>
       <c r="F82" t="n">
-        <v>861.97</v>
+        <v>16.41</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4019,11 +4019,11 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4040,34 +4040,34 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>男装</t>
+          <t>工具</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>254.22</v>
+        <v>202.72</v>
       </c>
       <c r="E83" t="n">
-        <v>424.09</v>
+        <v>269.66</v>
       </c>
       <c r="F83" t="n">
-        <v>292.35</v>
+        <v>233.13</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2024-08-31</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4084,22 +4084,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>零食</t>
+          <t>护肤</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>853.5700000000001</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="E84" t="n">
-        <v>1346.61</v>
+        <v>125.41</v>
       </c>
       <c r="F84" t="n">
-        <v>981.61</v>
+        <v>93.2</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -4128,34 +4128,34 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>洗护</t>
+          <t>数码</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>408.67</v>
+        <v>450.22</v>
       </c>
       <c r="E85" t="n">
-        <v>789.33</v>
+        <v>702.89</v>
       </c>
       <c r="F85" t="n">
-        <v>469.97</v>
+        <v>517.75</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2023-03-06</t>
+          <t>2023-03-29</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4172,22 +4172,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>饮料</t>
+          <t>辅食</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>864.59</v>
+        <v>170.44</v>
       </c>
       <c r="E86" t="n">
-        <v>1508.86</v>
+        <v>287.43</v>
       </c>
       <c r="F86" t="n">
-        <v>994.28</v>
+        <v>196.01</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4195,16 +4195,16 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -4221,29 +4221,29 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>童装</t>
+          <t>男装</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>200.03</v>
+        <v>243.65</v>
       </c>
       <c r="E87" t="n">
-        <v>389.35</v>
+        <v>325.71</v>
       </c>
       <c r="F87" t="n">
-        <v>230.03</v>
+        <v>280.2</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -4260,39 +4260,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>调味</t>
+          <t>男装</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>661.8099999999999</v>
+        <v>267.63</v>
       </c>
       <c r="E88" t="n">
-        <v>1159.76</v>
+        <v>434.24</v>
       </c>
       <c r="F88" t="n">
-        <v>761.08</v>
+        <v>307.77</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -4304,39 +4304,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>辅食</t>
+          <t>厨房</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>441.29</v>
+        <v>1676.89</v>
       </c>
       <c r="E89" t="n">
-        <v>841.85</v>
+        <v>2619.53</v>
       </c>
       <c r="F89" t="n">
-        <v>507.48</v>
+        <v>1928.42</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>季节性</t>
+          <t>在售</t>
         </is>
       </c>
     </row>
@@ -4353,17 +4353,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>纸品</t>
+          <t>洗护</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>821.83</v>
+        <v>24.82</v>
       </c>
       <c r="E90" t="n">
-        <v>1675.76</v>
+        <v>43.68</v>
       </c>
       <c r="F90" t="n">
-        <v>945.1</v>
+        <v>28.54</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4371,11 +4371,11 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -4392,34 +4392,34 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>小家电</t>
+          <t>女装</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>319.92</v>
+        <v>289.91</v>
       </c>
       <c r="E91" t="n">
-        <v>642.5599999999999</v>
+        <v>347.38</v>
       </c>
       <c r="F91" t="n">
-        <v>367.91</v>
+        <v>333.4</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2023-12-30</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -4436,26 +4436,26 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>生鲜</t>
+          <t>个护</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>279.9</v>
+        <v>922.0599999999999</v>
       </c>
       <c r="E92" t="n">
-        <v>459.86</v>
+        <v>1132.87</v>
       </c>
       <c r="F92" t="n">
-        <v>321.88</v>
+        <v>1060.37</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H92" t="n">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -4480,34 +4480,34 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>男装</t>
+          <t>香水</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1120.28</v>
+        <v>187.49</v>
       </c>
       <c r="E93" t="n">
-        <v>1582.23</v>
+        <v>227.68</v>
       </c>
       <c r="F93" t="n">
-        <v>1288.32</v>
+        <v>215.61</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4533,25 +4533,25 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>733.05</v>
+        <v>40.74</v>
       </c>
       <c r="E94" t="n">
-        <v>1232.99</v>
+        <v>55.22</v>
       </c>
       <c r="F94" t="n">
-        <v>843.01</v>
+        <v>46.85</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -4568,34 +4568,34 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>童装</t>
+          <t>饮料</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>394.02</v>
+        <v>30.29</v>
       </c>
       <c r="E95" t="n">
-        <v>678.39</v>
+        <v>44.67</v>
       </c>
       <c r="F95" t="n">
-        <v>453.12</v>
+        <v>34.83</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2023-02-15</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -4612,34 +4612,34 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>女装</t>
+          <t>香水</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>425.54</v>
+        <v>246.48</v>
       </c>
       <c r="E96" t="n">
-        <v>911.48</v>
+        <v>352.78</v>
       </c>
       <c r="F96" t="n">
-        <v>489.37</v>
+        <v>283.45</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -4656,39 +4656,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>零食</t>
+          <t>清洁</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>662.5</v>
+        <v>72.67</v>
       </c>
       <c r="E97" t="n">
-        <v>1367.47</v>
+        <v>86.34</v>
       </c>
       <c r="F97" t="n">
-        <v>761.87</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -4700,39 +4700,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>童装</t>
+          <t>用品</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>567.62</v>
+        <v>82.33</v>
       </c>
       <c r="E98" t="n">
-        <v>1046.79</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="F98" t="n">
-        <v>652.76</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2024-11-24</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -4744,26 +4744,26 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>生鲜</t>
+          <t>小家电</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>949.58</v>
+        <v>1008.52</v>
       </c>
       <c r="E99" t="n">
-        <v>1597.78</v>
+        <v>1342.18</v>
       </c>
       <c r="F99" t="n">
-        <v>1092.02</v>
+        <v>1159.8</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H99" t="n">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -4788,26 +4788,26 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>数码</t>
+          <t>奶粉</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>930.3099999999999</v>
+        <v>120.22</v>
       </c>
       <c r="E100" t="n">
-        <v>1921.67</v>
+        <v>153</v>
       </c>
       <c r="F100" t="n">
-        <v>1069.86</v>
+        <v>138.25</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H100" t="n">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -4832,34 +4832,34 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>玩具</t>
+          <t>香水</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>841.52</v>
+        <v>127.12</v>
       </c>
       <c r="E101" t="n">
-        <v>1485.12</v>
+        <v>196.9</v>
       </c>
       <c r="F101" t="n">
-        <v>967.75</v>
+        <v>146.19</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-02-09</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -4876,22 +4876,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>童装</t>
+          <t>玩具</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>866.45</v>
+        <v>284.13</v>
       </c>
       <c r="E102" t="n">
-        <v>1334.76</v>
+        <v>421</v>
       </c>
       <c r="F102" t="n">
-        <v>996.42</v>
+        <v>326.75</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -4899,16 +4899,16 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>季节性</t>
+          <t>在售</t>
         </is>
       </c>
     </row>
@@ -4920,22 +4920,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>女装</t>
+          <t>纸品</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>336</v>
+        <v>17.51</v>
       </c>
       <c r="E103" t="n">
-        <v>603.38</v>
+        <v>29.44</v>
       </c>
       <c r="F103" t="n">
-        <v>386.4</v>
+        <v>20.14</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -4943,16 +4943,16 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>停售</t>
         </is>
       </c>
     </row>
@@ -4964,39 +4964,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>童装</t>
+          <t>零食</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>545.92</v>
+        <v>17</v>
       </c>
       <c r="E104" t="n">
-        <v>1344.51</v>
+        <v>25.65</v>
       </c>
       <c r="F104" t="n">
-        <v>627.8099999999999</v>
+        <v>19.55</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>季节性</t>
+          <t>在售</t>
         </is>
       </c>
     </row>
@@ -5008,34 +5008,34 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>美妆</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>彩妆</t>
+          <t>用品</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>632.53</v>
+        <v>167.16</v>
       </c>
       <c r="E105" t="n">
-        <v>1257.56</v>
+        <v>215.32</v>
       </c>
       <c r="F105" t="n">
-        <v>727.41</v>
+        <v>192.23</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -5057,34 +5057,34 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>彩妆</t>
+          <t>护肤</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>125.7</v>
+        <v>122.09</v>
       </c>
       <c r="E106" t="n">
-        <v>232.11</v>
+        <v>176.42</v>
       </c>
       <c r="F106" t="n">
-        <v>144.55</v>
+        <v>140.4</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2023-01-11</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>停售</t>
         </is>
       </c>
     </row>
@@ -5096,34 +5096,34 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>家居</t>
+          <t>工具</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>924.9</v>
+        <v>117.65</v>
       </c>
       <c r="E107" t="n">
-        <v>1906.4</v>
+        <v>146.19</v>
       </c>
       <c r="F107" t="n">
-        <v>1063.63</v>
+        <v>135.3</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2023-04-11</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -5140,22 +5140,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>用品</t>
+          <t>配件</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>321.25</v>
+        <v>275.86</v>
       </c>
       <c r="E108" t="n">
-        <v>507.99</v>
+        <v>430.88</v>
       </c>
       <c r="F108" t="n">
-        <v>369.44</v>
+        <v>317.24</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -5193,30 +5193,30 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>346.77</v>
+        <v>178.49</v>
       </c>
       <c r="E109" t="n">
-        <v>655.3200000000001</v>
+        <v>234.16</v>
       </c>
       <c r="F109" t="n">
-        <v>398.79</v>
+        <v>205.26</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -5228,34 +5228,34 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>美妆</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>彩妆</t>
+          <t>洗护</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>963.48</v>
+        <v>34.4</v>
       </c>
       <c r="E110" t="n">
-        <v>1622.8</v>
+        <v>43.45</v>
       </c>
       <c r="F110" t="n">
-        <v>1108</v>
+        <v>39.56</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2023-01-02</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -5277,29 +5277,29 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>洗护</t>
+          <t>家居</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>175.52</v>
+        <v>18.73</v>
       </c>
       <c r="E111" t="n">
-        <v>337.34</v>
+        <v>22.72</v>
       </c>
       <c r="F111" t="n">
-        <v>201.85</v>
+        <v>21.54</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -5316,22 +5316,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>美妆</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>彩妆</t>
+          <t>女装</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>104.92</v>
+        <v>370.08</v>
       </c>
       <c r="E112" t="n">
-        <v>140.12</v>
+        <v>514.92</v>
       </c>
       <c r="F112" t="n">
-        <v>120.66</v>
+        <v>425.59</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -5343,12 +5343,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>季节性</t>
+          <t>在售</t>
         </is>
       </c>
     </row>
@@ -5360,34 +5360,34 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>小家电</t>
+          <t>用品</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1166.71</v>
+        <v>127.93</v>
       </c>
       <c r="E113" t="n">
-        <v>1968.68</v>
+        <v>152.24</v>
       </c>
       <c r="F113" t="n">
-        <v>1341.72</v>
+        <v>147.12</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -5404,34 +5404,34 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>清洁</t>
+          <t>厨房</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>649.72</v>
+        <v>2989.17</v>
       </c>
       <c r="E114" t="n">
-        <v>1241.98</v>
+        <v>4167.92</v>
       </c>
       <c r="F114" t="n">
-        <v>747.1799999999999</v>
+        <v>3437.55</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2024-08-17</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -5448,22 +5448,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>辅食</t>
+          <t>数码</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>865.35</v>
+        <v>1939.29</v>
       </c>
       <c r="E115" t="n">
-        <v>1548.55</v>
+        <v>3285.66</v>
       </c>
       <c r="F115" t="n">
-        <v>995.15</v>
+        <v>2230.18</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -5471,11 +5471,11 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -5492,34 +5492,34 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>辅食</t>
+          <t>男装</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>475.89</v>
+        <v>349.64</v>
       </c>
       <c r="E116" t="n">
-        <v>938.0599999999999</v>
+        <v>561.35</v>
       </c>
       <c r="F116" t="n">
-        <v>547.27</v>
+        <v>402.09</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -5541,34 +5541,34 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>彩妆</t>
+          <t>护肤</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>854.65</v>
+        <v>188.6</v>
       </c>
       <c r="E117" t="n">
-        <v>1777.97</v>
+        <v>308.68</v>
       </c>
       <c r="F117" t="n">
-        <v>982.85</v>
+        <v>216.89</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>停售</t>
+          <t>在售</t>
         </is>
       </c>
     </row>
@@ -5580,22 +5580,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>厨房</t>
+          <t>饮料</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>765.04</v>
+        <v>47.8</v>
       </c>
       <c r="E118" t="n">
-        <v>1172.56</v>
+        <v>64.25</v>
       </c>
       <c r="F118" t="n">
-        <v>879.8</v>
+        <v>54.97</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -5603,11 +5603,11 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -5624,34 +5624,34 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>美妆</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>工具</t>
+          <t>小家电</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>740.53</v>
+        <v>2408.26</v>
       </c>
       <c r="E119" t="n">
-        <v>1450.77</v>
+        <v>2913.21</v>
       </c>
       <c r="F119" t="n">
-        <v>851.61</v>
+        <v>2769.5</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -5668,34 +5668,34 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>生鲜</t>
+          <t>奶粉</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>527.1900000000001</v>
+        <v>224.15</v>
       </c>
       <c r="E120" t="n">
-        <v>798.76</v>
+        <v>278.74</v>
       </c>
       <c r="F120" t="n">
-        <v>606.27</v>
+        <v>257.77</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2023-03-27</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -5717,34 +5717,34 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>饮料</t>
+          <t>零食</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>607.73</v>
+        <v>27.3</v>
       </c>
       <c r="E121" t="n">
-        <v>829.3200000000001</v>
+        <v>47.25</v>
       </c>
       <c r="F121" t="n">
-        <v>698.89</v>
+        <v>31.39</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -5756,34 +5756,34 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>个护</t>
+          <t>清洁</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>216.69</v>
+        <v>91.89</v>
       </c>
       <c r="E122" t="n">
-        <v>337.76</v>
+        <v>119.75</v>
       </c>
       <c r="F122" t="n">
-        <v>249.19</v>
+        <v>105.67</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -5800,26 +5800,26 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>女装</t>
+          <t>洗护</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>649.59</v>
+        <v>42.26</v>
       </c>
       <c r="E123" t="n">
-        <v>1390.86</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F123" t="n">
-        <v>747.03</v>
+        <v>48.6</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H123" t="n">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -5844,22 +5844,22 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>童装</t>
+          <t>个护</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1179.19</v>
+        <v>609.1</v>
       </c>
       <c r="E124" t="n">
-        <v>1790.69</v>
+        <v>966</v>
       </c>
       <c r="F124" t="n">
-        <v>1356.07</v>
+        <v>700.46</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -5867,11 +5867,11 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -5888,34 +5888,34 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>饮料</t>
+          <t>香水</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>858.36</v>
+        <v>270.21</v>
       </c>
       <c r="E125" t="n">
-        <v>1727.86</v>
+        <v>359.27</v>
       </c>
       <c r="F125" t="n">
-        <v>987.11</v>
+        <v>310.74</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -5932,22 +5932,22 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>饮料</t>
+          <t>家居</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1077.29</v>
+        <v>59.06</v>
       </c>
       <c r="E126" t="n">
-        <v>1776.66</v>
+        <v>80.81</v>
       </c>
       <c r="F126" t="n">
-        <v>1238.88</v>
+        <v>67.92</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -5959,12 +5959,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>季节性</t>
+          <t>在售</t>
         </is>
       </c>
     </row>
@@ -5976,34 +5976,34 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>童装</t>
+          <t>饮料</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1044.35</v>
+        <v>10.32</v>
       </c>
       <c r="E127" t="n">
-        <v>1567.92</v>
+        <v>12.71</v>
       </c>
       <c r="F127" t="n">
-        <v>1201</v>
+        <v>11.87</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-06-04</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -6020,22 +6020,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>纸品</t>
+          <t>彩妆</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>290.28</v>
+        <v>123.46</v>
       </c>
       <c r="E128" t="n">
-        <v>476.74</v>
+        <v>203.58</v>
       </c>
       <c r="F128" t="n">
-        <v>333.82</v>
+        <v>141.98</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -6043,11 +6043,11 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -6064,34 +6064,34 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>男装</t>
+          <t>小家电</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1202.47</v>
+        <v>923.51</v>
       </c>
       <c r="E129" t="n">
-        <v>1618.01</v>
+        <v>1186.26</v>
       </c>
       <c r="F129" t="n">
-        <v>1382.84</v>
+        <v>1062.04</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2023-03-25</t>
+          <t>2023-01-26</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -6108,34 +6108,34 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>美妆</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>香水</t>
+          <t>家居</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>972.85</v>
+        <v>89.44</v>
       </c>
       <c r="E130" t="n">
-        <v>1407.03</v>
+        <v>116.56</v>
       </c>
       <c r="F130" t="n">
-        <v>1118.78</v>
+        <v>102.86</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2024-12-22</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -6152,34 +6152,34 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>纸品</t>
+          <t>厨房</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>481.46</v>
+        <v>1014.44</v>
       </c>
       <c r="E131" t="n">
-        <v>955.87</v>
+        <v>1413.55</v>
       </c>
       <c r="F131" t="n">
-        <v>553.6799999999999</v>
+        <v>1166.61</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -6201,34 +6201,34 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>护肤</t>
+          <t>香水</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>598.38</v>
+        <v>93.55</v>
       </c>
       <c r="E132" t="n">
-        <v>1136.94</v>
+        <v>134.83</v>
       </c>
       <c r="F132" t="n">
-        <v>688.14</v>
+        <v>107.58</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>停售</t>
+          <t>在售</t>
         </is>
       </c>
     </row>
@@ -6240,39 +6240,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>零食</t>
+          <t>彩妆</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>930.1900000000001</v>
+        <v>304.46</v>
       </c>
       <c r="E133" t="n">
-        <v>1839.07</v>
+        <v>375.49</v>
       </c>
       <c r="F133" t="n">
-        <v>1069.72</v>
+        <v>350.13</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -6284,22 +6284,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>清洁</t>
+          <t>工具</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>185.69</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="E134" t="n">
-        <v>286.65</v>
+        <v>149.19</v>
       </c>
       <c r="F134" t="n">
-        <v>213.54</v>
+        <v>111.5</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -6307,11 +6307,11 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2023-03-29</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -6328,26 +6328,26 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>美妆</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>工具</t>
+          <t>童装</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>137.74</v>
+        <v>124.79</v>
       </c>
       <c r="E135" t="n">
-        <v>310.01</v>
+        <v>149.07</v>
       </c>
       <c r="F135" t="n">
-        <v>158.4</v>
+        <v>143.51</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H135" t="n">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2024-12-22</t>
+          <t>2023-04-29</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -6372,22 +6372,22 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>美妆</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>香水</t>
+          <t>用品</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>397.65</v>
+        <v>167.15</v>
       </c>
       <c r="E136" t="n">
-        <v>956.05</v>
+        <v>301.38</v>
       </c>
       <c r="F136" t="n">
-        <v>457.3</v>
+        <v>192.22</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -6395,11 +6395,11 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -6416,39 +6416,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>纸品</t>
+          <t>男装</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>455</v>
+        <v>362.22</v>
       </c>
       <c r="E137" t="n">
-        <v>1085.71</v>
+        <v>435.81</v>
       </c>
       <c r="F137" t="n">
-        <v>523.25</v>
+        <v>416.55</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -6460,39 +6460,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>个护</t>
+          <t>生鲜</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>572.51</v>
+        <v>32.43</v>
       </c>
       <c r="E138" t="n">
-        <v>1139.9</v>
+        <v>38.67</v>
       </c>
       <c r="F138" t="n">
-        <v>658.39</v>
+        <v>37.29</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2023-05-26</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -6504,26 +6504,26 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>女装</t>
+          <t>护肤</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>488.46</v>
+        <v>158.56</v>
       </c>
       <c r="E139" t="n">
-        <v>668.73</v>
+        <v>270.95</v>
       </c>
       <c r="F139" t="n">
-        <v>561.73</v>
+        <v>182.34</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H139" t="n">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
+          <t>2023-12-23</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -6553,34 +6553,34 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>玩具</t>
+          <t>奶粉</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>949.05</v>
+        <v>303.63</v>
       </c>
       <c r="E140" t="n">
-        <v>1522.74</v>
+        <v>357.27</v>
       </c>
       <c r="F140" t="n">
-        <v>1091.41</v>
+        <v>349.17</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>停售</t>
         </is>
       </c>
     </row>
@@ -6597,17 +6597,17 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>工具</t>
+          <t>彩妆</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>605.77</v>
+        <v>185.45</v>
       </c>
       <c r="E141" t="n">
-        <v>913.02</v>
+        <v>267.34</v>
       </c>
       <c r="F141" t="n">
-        <v>696.64</v>
+        <v>213.27</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -6636,34 +6636,34 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>童装</t>
+          <t>辅食</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>714.5599999999999</v>
+        <v>101.45</v>
       </c>
       <c r="E142" t="n">
-        <v>1639.26</v>
+        <v>162.9</v>
       </c>
       <c r="F142" t="n">
-        <v>821.74</v>
+        <v>116.67</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -6680,39 +6680,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>奶粉</t>
+          <t>洗护</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>723.46</v>
+        <v>20.8</v>
       </c>
       <c r="E143" t="n">
-        <v>1789.44</v>
+        <v>28.44</v>
       </c>
       <c r="F143" t="n">
-        <v>831.98</v>
+        <v>23.92</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -6724,34 +6724,34 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>女装</t>
+          <t>调味</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>440.65</v>
+        <v>8.16</v>
       </c>
       <c r="E144" t="n">
-        <v>882.14</v>
+        <v>13.34</v>
       </c>
       <c r="F144" t="n">
-        <v>506.75</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>2024-01-13</t>
+          <t>2023-07-31</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -6768,34 +6768,34 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>调味</t>
+          <t>奶粉</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1032.02</v>
+        <v>282.91</v>
       </c>
       <c r="E145" t="n">
-        <v>1818.37</v>
+        <v>343.11</v>
       </c>
       <c r="F145" t="n">
-        <v>1186.82</v>
+        <v>325.35</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2023-07-08</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -6812,39 +6812,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>奶粉</t>
+          <t>调味</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>477.46</v>
+        <v>22.24</v>
       </c>
       <c r="E146" t="n">
-        <v>919.53</v>
+        <v>31.08</v>
       </c>
       <c r="F146" t="n">
-        <v>549.08</v>
+        <v>25.58</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>季节性</t>
+          <t>停售</t>
         </is>
       </c>
     </row>
@@ -6856,26 +6856,26 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>数码</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>265.92</v>
+        <v>865.75</v>
       </c>
       <c r="E147" t="n">
-        <v>360.36</v>
+        <v>1106.17</v>
       </c>
       <c r="F147" t="n">
-        <v>305.81</v>
+        <v>995.61</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H147" t="n">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-12-23</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -6905,29 +6905,29 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>彩妆</t>
+          <t>香水</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>844.84</v>
+        <v>60.41</v>
       </c>
       <c r="E148" t="n">
-        <v>1729.92</v>
+        <v>90.95</v>
       </c>
       <c r="F148" t="n">
-        <v>971.5700000000001</v>
+        <v>69.47</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -6944,22 +6944,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>奶粉</t>
+          <t>纸品</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>650.84</v>
+        <v>34.11</v>
       </c>
       <c r="E149" t="n">
-        <v>927.64</v>
+        <v>48.03</v>
       </c>
       <c r="F149" t="n">
-        <v>748.47</v>
+        <v>39.23</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -6967,11 +6967,11 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2023-04-10</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -6988,26 +6988,26 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>饮料</t>
+          <t>小家电</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>666.92</v>
+        <v>1525.76</v>
       </c>
       <c r="E150" t="n">
-        <v>1515.96</v>
+        <v>2319.56</v>
       </c>
       <c r="F150" t="n">
-        <v>766.96</v>
+        <v>1754.62</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H150" t="n">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -7032,26 +7032,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>清洁</t>
+          <t>玩具</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>713.6900000000001</v>
+        <v>176.16</v>
       </c>
       <c r="E151" t="n">
-        <v>1687.73</v>
+        <v>280.3</v>
       </c>
       <c r="F151" t="n">
-        <v>820.74</v>
+        <v>202.58</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H151" t="n">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2023-03-25</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -7076,26 +7076,26 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>美妆</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>护肤</t>
+          <t>男装</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>337.98</v>
+        <v>162.42</v>
       </c>
       <c r="E152" t="n">
-        <v>590.76</v>
+        <v>230.76</v>
       </c>
       <c r="F152" t="n">
-        <v>388.68</v>
+        <v>186.78</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H152" t="n">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-12-14</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -7120,22 +7120,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>调味</t>
+          <t>用品</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>942.95</v>
+        <v>137.27</v>
       </c>
       <c r="E153" t="n">
-        <v>1566.47</v>
+        <v>196.33</v>
       </c>
       <c r="F153" t="n">
-        <v>1084.39</v>
+        <v>157.86</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -7143,16 +7143,16 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -7164,34 +7164,34 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>生鲜</t>
+          <t>彩妆</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>637.03</v>
+        <v>78.39</v>
       </c>
       <c r="E154" t="n">
-        <v>994.96</v>
+        <v>135.25</v>
       </c>
       <c r="F154" t="n">
-        <v>732.58</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -7217,25 +7217,25 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>234.04</v>
+        <v>61.67</v>
       </c>
       <c r="E155" t="n">
-        <v>516.53</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="F155" t="n">
-        <v>269.15</v>
+        <v>70.92</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H155" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2023-03-04</t>
+          <t>2023-03-10</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -7252,22 +7252,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>童装</t>
+          <t>生鲜</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>620.8099999999999</v>
+        <v>53.34</v>
       </c>
       <c r="E156" t="n">
-        <v>907.75</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="F156" t="n">
-        <v>713.9299999999999</v>
+        <v>61.34</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -7275,11 +7275,11 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -7296,34 +7296,34 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>清洁</t>
+          <t>辅食</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1055.39</v>
+        <v>123.09</v>
       </c>
       <c r="E157" t="n">
-        <v>1441.41</v>
+        <v>153.49</v>
       </c>
       <c r="F157" t="n">
-        <v>1213.7</v>
+        <v>141.55</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H157" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2023-02-15</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -7349,17 +7349,17 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>218.03</v>
+        <v>317.73</v>
       </c>
       <c r="E158" t="n">
-        <v>507.26</v>
+        <v>385.45</v>
       </c>
       <c r="F158" t="n">
-        <v>250.73</v>
+        <v>365.39</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H158" t="n">
@@ -7367,7 +7367,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -7389,21 +7389,21 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>彩妆</t>
+          <t>香水</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>343.19</v>
+        <v>129.97</v>
       </c>
       <c r="E159" t="n">
-        <v>704.9</v>
+        <v>196.57</v>
       </c>
       <c r="F159" t="n">
-        <v>394.67</v>
+        <v>149.47</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H159" t="n">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -7433,29 +7433,29 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>女装</t>
+          <t>配件</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1066.47</v>
+        <v>350.2</v>
       </c>
       <c r="E160" t="n">
-        <v>1791.4</v>
+        <v>519.45</v>
       </c>
       <c r="F160" t="n">
-        <v>1226.44</v>
+        <v>402.73</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H160" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -7481,30 +7481,30 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>113.02</v>
+        <v>62.31</v>
       </c>
       <c r="E161" t="n">
-        <v>207.13</v>
+        <v>86.69</v>
       </c>
       <c r="F161" t="n">
-        <v>129.97</v>
+        <v>71.66</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H161" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2023-01-24</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -7516,22 +7516,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>辅食</t>
+          <t>清洁</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>209.45</v>
+        <v>40.79</v>
       </c>
       <c r="E162" t="n">
-        <v>344.12</v>
+        <v>66.17</v>
       </c>
       <c r="F162" t="n">
-        <v>240.87</v>
+        <v>46.91</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -7539,16 +7539,16 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>季节性</t>
+          <t>在售</t>
         </is>
       </c>
     </row>
@@ -7560,34 +7560,34 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>美妆</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>工具</t>
+          <t>清洁</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>491.26</v>
+        <v>47.87</v>
       </c>
       <c r="E163" t="n">
-        <v>796.92</v>
+        <v>80.62</v>
       </c>
       <c r="F163" t="n">
-        <v>564.95</v>
+        <v>55.05</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H163" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>2023-05-29</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -7604,22 +7604,22 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>清洁</t>
+          <t>小家电</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>233.66</v>
+        <v>1498.26</v>
       </c>
       <c r="E164" t="n">
-        <v>347.97</v>
+        <v>2384.89</v>
       </c>
       <c r="F164" t="n">
-        <v>268.71</v>
+        <v>1723</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -7627,16 +7627,16 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>停售</t>
         </is>
       </c>
     </row>
@@ -7648,34 +7648,34 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>用品</t>
+          <t>家居</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>249.08</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="E165" t="n">
-        <v>467.21</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="F165" t="n">
-        <v>286.44</v>
+        <v>92.33</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H165" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -7692,22 +7692,22 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>奶粉</t>
+          <t>小家电</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>616.73</v>
+        <v>299.19</v>
       </c>
       <c r="E166" t="n">
-        <v>858.99</v>
+        <v>413.39</v>
       </c>
       <c r="F166" t="n">
-        <v>709.24</v>
+        <v>344.07</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -7719,12 +7719,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2024-11-24</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>停售</t>
         </is>
       </c>
     </row>
@@ -7736,34 +7736,34 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>美妆</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>护肤</t>
+          <t>辅食</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>350.44</v>
+        <v>98.31</v>
       </c>
       <c r="E167" t="n">
-        <v>695.22</v>
+        <v>145.59</v>
       </c>
       <c r="F167" t="n">
-        <v>403.01</v>
+        <v>113.06</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H167" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -7789,17 +7789,17 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>580.87</v>
+        <v>545.35</v>
       </c>
       <c r="E168" t="n">
-        <v>958.55</v>
+        <v>915.4400000000001</v>
       </c>
       <c r="F168" t="n">
-        <v>668</v>
+        <v>627.15</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H168" t="n">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2023-06-18</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -7824,34 +7824,34 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>个护</t>
+          <t>护肤</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>94.3</v>
+        <v>52.58</v>
       </c>
       <c r="E169" t="n">
-        <v>171.42</v>
+        <v>81.02</v>
       </c>
       <c r="F169" t="n">
-        <v>108.44</v>
+        <v>60.47</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H169" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>2023-03-20</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -7868,39 +7868,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>美妆</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>香水</t>
+          <t>数码</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1002.84</v>
+        <v>808.25</v>
       </c>
       <c r="E170" t="n">
-        <v>1674.14</v>
+        <v>1217.33</v>
       </c>
       <c r="F170" t="n">
-        <v>1153.27</v>
+        <v>929.49</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H170" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -7912,39 +7912,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>饮料</t>
+          <t>奶粉</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>340.86</v>
+        <v>192.39</v>
       </c>
       <c r="E171" t="n">
-        <v>809.48</v>
+        <v>240.49</v>
       </c>
       <c r="F171" t="n">
-        <v>391.99</v>
+        <v>221.25</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H171" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -7956,22 +7956,22 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>零食</t>
+          <t>配件</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1141.67</v>
+        <v>318.22</v>
       </c>
       <c r="E172" t="n">
-        <v>1551.1</v>
+        <v>454.74</v>
       </c>
       <c r="F172" t="n">
-        <v>1312.92</v>
+        <v>365.95</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -7979,16 +7979,16 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>季节性</t>
+          <t>在售</t>
         </is>
       </c>
     </row>
@@ -8000,34 +8000,34 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>辅食</t>
+          <t>数码</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>823.74</v>
+        <v>2334.95</v>
       </c>
       <c r="E173" t="n">
-        <v>1894.82</v>
+        <v>3128.36</v>
       </c>
       <c r="F173" t="n">
-        <v>947.3</v>
+        <v>2685.19</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H173" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -8044,26 +8044,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>数码</t>
+          <t>男装</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>58.75</v>
+        <v>341.19</v>
       </c>
       <c r="E174" t="n">
-        <v>88.09</v>
+        <v>451.64</v>
       </c>
       <c r="F174" t="n">
-        <v>67.56</v>
+        <v>392.37</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H174" t="n">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>停售</t>
+          <t>在售</t>
         </is>
       </c>
     </row>
@@ -8088,22 +8088,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>美妆</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>香水</t>
+          <t>辅食</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1093.82</v>
+        <v>271.33</v>
       </c>
       <c r="E175" t="n">
-        <v>1767.28</v>
+        <v>432.61</v>
       </c>
       <c r="F175" t="n">
-        <v>1257.89</v>
+        <v>312.03</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -8111,11 +8111,11 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -8132,34 +8132,34 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>生鲜</t>
+          <t>清洁</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>577.65</v>
+        <v>35.47</v>
       </c>
       <c r="E176" t="n">
-        <v>1172.6</v>
+        <v>44.53</v>
       </c>
       <c r="F176" t="n">
-        <v>664.3</v>
+        <v>40.79</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H176" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>2023-01-16</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -8176,34 +8176,34 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>调味</t>
+          <t>家居</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>419.89</v>
+        <v>12.91</v>
       </c>
       <c r="E177" t="n">
-        <v>980.11</v>
+        <v>15.37</v>
       </c>
       <c r="F177" t="n">
-        <v>482.87</v>
+        <v>14.85</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H177" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -8220,34 +8220,34 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>美妆</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>护肤</t>
+          <t>玩具</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>913.87</v>
+        <v>287.57</v>
       </c>
       <c r="E178" t="n">
-        <v>1888.35</v>
+        <v>387.29</v>
       </c>
       <c r="F178" t="n">
-        <v>1050.95</v>
+        <v>330.71</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H178" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -8264,34 +8264,34 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>纸品</t>
+          <t>男装</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>375.07</v>
+        <v>230.31</v>
       </c>
       <c r="E179" t="n">
-        <v>632.29</v>
+        <v>330.35</v>
       </c>
       <c r="F179" t="n">
-        <v>431.33</v>
+        <v>264.86</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H179" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>2023-02-22</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -8308,34 +8308,34 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>奶粉</t>
+          <t>饮料</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>368.59</v>
+        <v>12.14</v>
       </c>
       <c r="E180" t="n">
-        <v>810.47</v>
+        <v>20.22</v>
       </c>
       <c r="F180" t="n">
-        <v>423.88</v>
+        <v>13.96</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H180" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>2023-06-03</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -8352,26 +8352,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>美妆</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>彩妆</t>
+          <t>童装</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>971.23</v>
+        <v>592.84</v>
       </c>
       <c r="E181" t="n">
-        <v>1788.7</v>
+        <v>751.87</v>
       </c>
       <c r="F181" t="n">
-        <v>1116.91</v>
+        <v>681.77</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H181" t="n">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2024-02-19</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -8396,22 +8396,22 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>清洁</t>
+          <t>小家电</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1077.14</v>
+        <v>521.62</v>
       </c>
       <c r="E182" t="n">
-        <v>1679.67</v>
+        <v>868.24</v>
       </c>
       <c r="F182" t="n">
-        <v>1238.71</v>
+        <v>599.86</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -8440,26 +8440,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>玩具</t>
+          <t>男装</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>620.65</v>
+        <v>225.13</v>
       </c>
       <c r="E183" t="n">
-        <v>1099.53</v>
+        <v>293.87</v>
       </c>
       <c r="F183" t="n">
-        <v>713.75</v>
+        <v>258.9</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H183" t="n">
@@ -8467,7 +8467,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>2024-01-23</t>
+          <t>2023-07-08</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -8484,34 +8484,34 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>小家电</t>
+          <t>辅食</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>609.95</v>
+        <v>172.33</v>
       </c>
       <c r="E184" t="n">
-        <v>1482.54</v>
+        <v>247.42</v>
       </c>
       <c r="F184" t="n">
-        <v>701.4400000000001</v>
+        <v>198.18</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H184" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2023-07-10</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -8528,34 +8528,34 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>女装</t>
+          <t>工具</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>806.22</v>
+        <v>179.52</v>
       </c>
       <c r="E185" t="n">
-        <v>1609.74</v>
+        <v>217.58</v>
       </c>
       <c r="F185" t="n">
-        <v>927.15</v>
+        <v>206.45</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H185" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>2024-01-19</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -8572,34 +8572,34 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>奶粉</t>
+          <t>生鲜</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>898.48</v>
+        <v>17.62</v>
       </c>
       <c r="E186" t="n">
-        <v>1800.73</v>
+        <v>24.72</v>
       </c>
       <c r="F186" t="n">
-        <v>1033.25</v>
+        <v>20.26</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H186" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -8616,22 +8616,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>小家电</t>
+          <t>配件</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>702.3</v>
+        <v>403.01</v>
       </c>
       <c r="E187" t="n">
-        <v>1002.05</v>
+        <v>542.74</v>
       </c>
       <c r="F187" t="n">
-        <v>807.64</v>
+        <v>463.46</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -8639,11 +8639,11 @@
         </is>
       </c>
       <c r="H187" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -8660,22 +8660,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>零食</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>247.39</v>
+        <v>12.47</v>
       </c>
       <c r="E188" t="n">
-        <v>582.22</v>
+        <v>21.97</v>
       </c>
       <c r="F188" t="n">
-        <v>284.5</v>
+        <v>14.34</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -8683,11 +8683,11 @@
         </is>
       </c>
       <c r="H188" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -8709,17 +8709,17 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>饮料</t>
+          <t>零食</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>480.25</v>
+        <v>34.98</v>
       </c>
       <c r="E189" t="n">
-        <v>997</v>
+        <v>62.45</v>
       </c>
       <c r="F189" t="n">
-        <v>552.29</v>
+        <v>40.23</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -8727,11 +8727,11 @@
         </is>
       </c>
       <c r="H189" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2023-01-30</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -8748,26 +8748,26 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>零食</t>
+          <t>女装</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>398.15</v>
+        <v>652.35</v>
       </c>
       <c r="E190" t="n">
-        <v>808.27</v>
+        <v>811.37</v>
       </c>
       <c r="F190" t="n">
-        <v>457.87</v>
+        <v>750.2</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H190" t="n">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2025-01-25</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -8792,34 +8792,34 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>调味</t>
+          <t>配件</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>916.78</v>
+        <v>364.01</v>
       </c>
       <c r="E191" t="n">
-        <v>1354.3</v>
+        <v>436.7</v>
       </c>
       <c r="F191" t="n">
-        <v>1054.3</v>
+        <v>418.61</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H191" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -8836,34 +8836,34 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>母婴</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>辅食</t>
+          <t>洗护</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>974.15</v>
+        <v>52.93</v>
       </c>
       <c r="E192" t="n">
-        <v>1606.38</v>
+        <v>70.53</v>
       </c>
       <c r="F192" t="n">
-        <v>1120.27</v>
+        <v>60.87</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H192" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -8880,34 +8880,34 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>服饰</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>洗护</t>
+          <t>男装</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>996.26</v>
+        <v>179.78</v>
       </c>
       <c r="E193" t="n">
-        <v>1462.15</v>
+        <v>230.69</v>
       </c>
       <c r="F193" t="n">
-        <v>1145.7</v>
+        <v>206.75</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H193" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2023-07-22</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -8929,29 +8929,29 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>男装</t>
+          <t>配件</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>792.54</v>
+        <v>639.74</v>
       </c>
       <c r="E194" t="n">
-        <v>1688.99</v>
+        <v>949.5700000000001</v>
       </c>
       <c r="F194" t="n">
-        <v>911.42</v>
+        <v>735.7</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H194" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -8968,34 +8968,34 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>食品</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>零食</t>
+          <t>清洁</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>811.28</v>
+        <v>24.1</v>
       </c>
       <c r="E195" t="n">
-        <v>1843.11</v>
+        <v>30.02</v>
       </c>
       <c r="F195" t="n">
-        <v>932.97</v>
+        <v>27.71</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H195" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -9012,34 +9012,34 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>美妆</t>
+          <t>日用</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>护肤</t>
+          <t>清洁</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>939.37</v>
+        <v>40.41</v>
       </c>
       <c r="E196" t="n">
-        <v>1962.41</v>
+        <v>65.23</v>
       </c>
       <c r="F196" t="n">
-        <v>1080.28</v>
+        <v>46.47</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H196" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -9056,39 +9056,39 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>服饰</t>
+          <t>美妆</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>童装</t>
+          <t>香水</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>493.54</v>
+        <v>310.52</v>
       </c>
       <c r="E197" t="n">
-        <v>1091.54</v>
+        <v>407.43</v>
       </c>
       <c r="F197" t="n">
-        <v>567.5700000000001</v>
+        <v>357.1</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H197" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>季节性</t>
         </is>
       </c>
     </row>
@@ -9105,17 +9105,17 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>配件</t>
+          <t>童装</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>896.47</v>
+        <v>139.97</v>
       </c>
       <c r="E198" t="n">
-        <v>1818.51</v>
+        <v>253.22</v>
       </c>
       <c r="F198" t="n">
-        <v>1030.94</v>
+        <v>160.97</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>2023-03-18</t>
+          <t>2023-01-05</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -9144,34 +9144,34 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>纸品</t>
+          <t>数码</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>541.62</v>
+        <v>1170.05</v>
       </c>
       <c r="E199" t="n">
-        <v>1204.19</v>
+        <v>1667.41</v>
       </c>
       <c r="F199" t="n">
-        <v>622.86</v>
+        <v>1345.56</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H199" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2024-12-22</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -9188,34 +9188,34 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>个护</t>
+          <t>调味</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>565.17</v>
+        <v>14.5</v>
       </c>
       <c r="E200" t="n">
-        <v>1342.85</v>
+        <v>21.91</v>
       </c>
       <c r="F200" t="n">
-        <v>649.95</v>
+        <v>16.67</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H200" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -9232,22 +9232,22 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>日用</t>
+          <t>母婴</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>洗护</t>
+          <t>用品</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>144.76</v>
+        <v>251.75</v>
       </c>
       <c r="E201" t="n">
-        <v>213.7</v>
+        <v>342.35</v>
       </c>
       <c r="F201" t="n">
-        <v>166.47</v>
+        <v>289.51</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -9255,11 +9255,11 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-07-30</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
